--- a/test/fixtures/files/Sara-Alert-Format-Invalid-Monitorees.xlsx
+++ b/test/fixtures/files/Sara-Alert-Format-Invalid-Monitorees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twong/Documents/SARA-ALERT/SaraAlert/test/fixtures/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA6BDB1-A898-2D43-97A0-422D75C4473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4BDB78-C5D6-1647-83A2-5EC38D68F0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="29040" windowHeight="15840" xr2:uid="{FB22F82A-CCC1-4D6A-91C1-F71C3D0DC51F}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="33600" windowHeight="20540" xr2:uid="{FB22F82A-CCC1-4D6A-91C1-F71C3D0DC51F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>Middle Name</t>
   </si>
@@ -367,6 +367,12 @@
   </si>
   <si>
     <t>Vaccine 2 Notes</t>
+  </si>
+  <si>
+    <t>Follow-Up Reason</t>
+  </si>
+  <si>
+    <t>Follow-Up Note</t>
   </si>
 </sst>
 </file>
@@ -722,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E0A48AF-1FB5-45BC-B992-E199F2EDE988}">
-  <dimension ref="A1:DH1"/>
+  <dimension ref="A1:DJ1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -837,10 +843,12 @@
     <col min="110" max="110" width="24.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="111" max="111" width="19.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="112" max="112" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="113" max="16384" width="11.83203125" style="1"/>
+    <col min="113" max="113" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="114" max="114" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="115" max="16384" width="11.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:112" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>83</v>
       </c>
@@ -1176,6 +1184,12 @@
       </c>
       <c r="DH1" t="s">
         <v>111</v>
+      </c>
+      <c r="DI1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1185,9 +1199,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1388,27 +1405,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB466D0-FDD2-42B9-89BA-6A1D062B643C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{466812D3-9823-4964-8A86-52E723D24896}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="23e9cf30-ef1f-414a-92de-e987813e3346"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f188c146-715c-4d6d-ba0d-f71ec86e1ad8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1433,9 +1438,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{466812D3-9823-4964-8A86-52E723D24896}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EB466D0-FDD2-42B9-89BA-6A1D062B643C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="23e9cf30-ef1f-414a-92de-e987813e3346"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f188c146-715c-4d6d-ba0d-f71ec86e1ad8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>